--- a/wishbunny_latest.xlsx
+++ b/wishbunny_latest.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E169"/>
+  <dimension ref="A1:F169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,11 @@
           <t>link</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>status_note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -463,22 +468,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>주니식기 전구성</t>
+          <t>키미티즈방수네임시리즈</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>02.02 ~ 02.04</t>
+          <t>02.03</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9151</t>
+          <t>https://www.wishbunny.me/drop/9894</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -490,7 +500,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>타이니코스모스 낮잠이불</t>
+          <t>간편식 &amp; 간식</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -500,12 +510,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>02.12 ~ 02.20</t>
+          <t>02.03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9147</t>
+          <t>https://www.wishbunny.me/drop/9893</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -517,22 +532,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>지노키오 낮잠이불</t>
+          <t>물컵 총판</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>21,000</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>02.04 ~ 02.08</t>
+          <t>02.02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9140</t>
+          <t>https://www.wishbunny.me/drop/9892</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -544,7 +564,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>마이키즈</t>
+          <t>치약 칫솔 바디워시</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,12 +574,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>02.23 ~ 02.28</t>
+          <t>02.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9134</t>
+          <t>https://www.wishbunny.me/drop/9891</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -571,22 +596,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>탁가온</t>
+          <t>외출전 엘리베어 손소독티슈</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>51,000</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>02.14 ~ 02.18</t>
+          <t>02.02 ~ 02.06</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9132</t>
+          <t>https://www.wishbunny.me/drop/9890</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -598,22 +628,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>푸른들</t>
+          <t>배도라지즙/배숙</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>38,700</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>02.09 ~ 02.12</t>
+          <t>02.02 ~ 02.04</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9131</t>
+          <t>https://www.wishbunny.me/drop/9888</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -625,22 +660,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>사다리 변기 1세대</t>
+          <t>NEW 뉴이 클라우드 부스터</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>24,800</t>
+          <t>49,800</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>01.30 ~ 02.02</t>
+          <t>02.04 ~ 02.08</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9126</t>
+          <t>https://www.wishbunny.me/drop/9887</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -652,22 +692,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>사다리 변기 2세대 plus</t>
+          <t>MULNORY 채소 실리콘 장난감 주방놀이</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>28,900</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>01.30 ~ 02.02</t>
+          <t>02.05 ~ 02.10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9125</t>
+          <t>https://www.wishbunny.me/drop/9886</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -679,22 +724,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>명절연휴 대비육아템❤ 노래하는가방스티커</t>
+          <t>헬시올라잇 이유식 팩토리</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>39,800</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>02.05 ~ 02.09</t>
+          <t>02.02 ~ 02.08</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9119</t>
+          <t>https://www.wishbunny.me/drop/9881</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -706,22 +756,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>슬라임12종랜덤박스/20종슬라임키트</t>
+          <t>바이오메라 키즈 유산균 비타민D 아연</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>34,430</t>
+          <t>58,000</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>01.30</t>
+          <t>02.02 ~ 02.08</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9118</t>
+          <t>https://www.wishbunny.me/drop/9880</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -733,22 +788,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>수혁맘특가</t>
+          <t>EQ의천재들 이큐의천재들</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3,900</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>01.30</t>
+          <t>02.02 ~ 02.09</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9115</t>
+          <t>https://www.wishbunny.me/drop/9879</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -760,22 +820,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>수혁맘특가두조각퍼즐</t>
+          <t>명절 자수네임 복주머니</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>10,500</t>
+          <t>13,500</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>01.30</t>
+          <t>02.02 ~ 02.06</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9114</t>
+          <t>https://www.wishbunny.me/drop/9878</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -787,7 +852,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>안아주기 &amp; 엄마 마음 &amp; 아이 마음 그림책 최저가</t>
+          <t>엉덩이탐정 시리즈</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -797,12 +862,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>01.30</t>
+          <t>02.20 ~ 02.22</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9153</t>
+          <t>https://www.wishbunny.me/drop/9870</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -814,22 +884,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Why고전 29권 세트</t>
+          <t>나의 첫 지리책</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>175,500</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>01.30</t>
+          <t>02.02 ~ 02.04</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9150</t>
+          <t>https://www.wishbunny.me/drop/9863</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -841,22 +916,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>잉글리쉬 송즈 사운드북</t>
+          <t>엄마마음그림책</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>9,600</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>01.30 ~ 02.05</t>
+          <t>01.28 ~ 02.03</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9124</t>
+          <t>https://www.wishbunny.me/drop/9852</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -868,22 +948,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>시리즈 Why 피플 49권 세트</t>
+          <t>어떡해요</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>252,500</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>01.30</t>
+          <t>02.27</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9123</t>
+          <t>https://www.wishbunny.me/drop/9850</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -895,22 +980,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Why 초등 교과서 연계 (예비 초등 포함)</t>
+          <t>우리그림책/ 새계그림책</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>25,200</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>01.30</t>
+          <t>02.25</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9122</t>
+          <t>https://www.wishbunny.me/drop/9849</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -922,22 +1012,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>EQ의 천재들 115종 &amp; 모험시리즈 &amp; 매일시리즈 최저가!</t>
+          <t>345처음한글세트</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>246,000</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>01.30</t>
+          <t>02.23</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9121</t>
+          <t>https://www.wishbunny.me/drop/9847</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -949,22 +1044,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>키움 입학준비끝내기4종</t>
+          <t>튼튼곰시리즈</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>31,200</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>01.30</t>
+          <t>02.09</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9120</t>
+          <t>https://www.wishbunny.me/drop/9843</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -976,22 +1076,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>물아저씨 특별판4권</t>
+          <t>공룡대발이 시리즈(생활동화/성교육동화/유치원동화)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>88,200</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>01.30 ~ 02.28</t>
+          <t>02.01 ~ 02.08</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9117</t>
+          <t>https://www.wishbunny.me/drop/9836</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1108,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>블루래빗 명작</t>
+          <t>코리생활동화</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1013,12 +1118,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>02.10 ~ 02.13</t>
+          <t>02.23 ~ 02.25</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9064</t>
+          <t>https://www.wishbunny.me/drop/9810</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1030,7 +1140,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>토토랑 짝짝짝 생활동화</t>
+          <t>블루래빗 골라담기</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1040,12 +1150,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>02.02 ~ 02.05</t>
+          <t>02.04 ~ 02.06</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9050</t>
+          <t>https://www.wishbunny.me/drop/9799</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1057,22 +1172,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>why수학최저가</t>
+          <t>망고라이언 어떡해요</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>94,900</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>01.30 ~ 02.04</t>
+          <t>02.16 ~ 02.18</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9013</t>
+          <t>https://www.wishbunny.me/drop/9725</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1084,22 +1204,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>비밀요원레너드최저가</t>
+          <t>[천개의 바람] 한국사 2차</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>55,500</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>01.29 ~ 02.03</t>
+          <t>02.19 ~ 03.25</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9012</t>
+          <t>https://www.wishbunny.me/drop/9708</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1111,22 +1236,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>사파cd/dvd씨디플레이어최저가공구중</t>
+          <t>노부영 마.퍼.디</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>01.30</t>
+          <t>02.23 ~ 02.25</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9154</t>
+          <t>https://www.wishbunny.me/drop/9871</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1268,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>몬스터매그 챌린지</t>
+          <t>첫시작 낱말카드</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1148,12 +1278,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>02.23 ~ 02.25</t>
+          <t>02.12 ~ 02.14</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9086</t>
+          <t>https://www.wishbunny.me/drop/9868</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1300,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>보드게임 기획적</t>
+          <t>학습보드게임</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1175,12 +1310,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>02.02 ~ 02.04</t>
+          <t>02.09 ~ 02.11</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9084</t>
+          <t>https://www.wishbunny.me/drop/9867</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1332,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>레벨릭스 워크북 전체</t>
+          <t>글자놀이세트</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1202,12 +1342,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>02.20 ~ 02.22</t>
+          <t>02.20</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9055</t>
+          <t>https://www.wishbunny.me/drop/9846</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1219,22 +1364,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>실리콘 블럭 모음전</t>
+          <t>슈퍼매직파닉스</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>02.04 ~ 02.07</t>
+          <t>02.05</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8973</t>
+          <t>https://www.wishbunny.me/drop/9841</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1396,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>만능 토츠 독서대 3 in 1</t>
+          <t>한글 자석 글자 교구세트</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>37,900</t>
+          <t>22,700</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>01.29 ~ 02.01</t>
+          <t>02.02 ~ 02.06</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8966</t>
+          <t>https://www.wishbunny.me/drop/9832</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1273,22 +1428,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>패턴 플레이 EVA 입체 스티커놀이</t>
+          <t>요미펜</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>02.07 ~ 02.11</t>
+          <t>02.24 ~ 02.27</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8924</t>
+          <t>https://www.wishbunny.me/drop/9829</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1300,22 +1460,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>크레욜라 메스프리 모음전</t>
+          <t>블루레빗 워크북</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>02.09 ~ 02.12</t>
+          <t>02.09 ~ 02.11</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8919</t>
+          <t>https://www.wishbunny.me/drop/9825</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1492,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>썼다 지웠다 워크북</t>
+          <t>칠교</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1337,12 +1502,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>01.27 ~ 01.29</t>
+          <t>02.02 ~ 02.04</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8908</t>
+          <t>https://www.wishbunny.me/drop/9823</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1354,22 +1524,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>복합기 (코팅+열제본)</t>
+          <t>쑥쑥이차트</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>02.02 ~ 02.06</t>
+          <t>02.27 ~ 03.01</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8902</t>
+          <t>https://www.wishbunny.me/drop/9813</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1381,22 +1556,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>어린이집 자수네임 고리수건/자수네임 방수파우치(체크/투명)</t>
+          <t>수학용어 총정리</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>01.25 ~ 02.01</t>
+          <t>02.23 ~ 02.25</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8868</t>
+          <t>https://www.wishbunny.me/drop/9770</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1408,22 +1588,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>요미몬</t>
+          <t>그림으로 보는 한국사 외</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>84,000</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>01.27 ~ 01.30</t>
+          <t>02.04 ~ 02.06</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8822</t>
+          <t>https://www.wishbunny.me/drop/9767</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1620,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>함안 할매곶감</t>
+          <t>마이쿠커</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1445,12 +1630,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>02.04 ~ 02.05</t>
+          <t>02.06 ~ 02.09</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9144</t>
+          <t>https://www.wishbunny.me/drop/9889</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1652,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>올바름과자</t>
+          <t>도멘 아도니스 올리브오일</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1472,12 +1662,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>02.25 ~ 02.28</t>
+          <t>02.03 ~ 02.08</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9135</t>
+          <t>https://www.wishbunny.me/drop/9882</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1684,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>바맘 배도라지즙</t>
+          <t>방토즙/ 단호박즙</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1499,12 +1694,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>02.05 ~ 02.06</t>
+          <t>02.04 ~ 02.06</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9130</t>
+          <t>https://www.wishbunny.me/drop/9865</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1516,22 +1716,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>영덕대게키토산어묵</t>
+          <t>신라명과</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>01.29 ~ 02.27</t>
+          <t>02.03 ~ 02.05</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9108</t>
+          <t>https://www.wishbunny.me/drop/9864</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1748,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>홍익 쭈꾸미</t>
+          <t>그래인스쿠키</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1553,12 +1758,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>02.23 ~ 02.25</t>
+          <t>02.03</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9094</t>
+          <t>https://www.wishbunny.me/drop/9840</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1570,22 +1780,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>나는 레몬이에오/ 우린 레몬생강이에오</t>
+          <t>두바이쫀득쿠키 4구 선물세트</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>27,900</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>02.16 ~ 02.18</t>
+          <t>02.02 ~ 02.14</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9092</t>
+          <t>https://www.wishbunny.me/drop/9837</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1812,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>너티버티</t>
+          <t>빼빼구마</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1607,12 +1822,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>02.12 ~ 02.15</t>
+          <t>02.26 ~ 02.28</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9091</t>
+          <t>https://www.wishbunny.me/drop/9831</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1844,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>느티나무 소갈비찜 선물세트</t>
+          <t>(신키네도) 롤케이크</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1634,12 +1854,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>02.09 ~ 02.11</t>
+          <t>02.04 ~ 02.07</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9090</t>
+          <t>https://www.wishbunny.me/drop/9817</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1651,22 +1876,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>미다온 앙금가래떡 선물세트</t>
+          <t>(단시아)반건시</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>46,900</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>02.09 ~ 02.11</t>
+          <t>02.02 ~ 02.07</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9089</t>
+          <t>https://www.wishbunny.me/drop/9815</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1678,7 +1908,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>김부각 선물세트</t>
+          <t>모찌당 딸기모찌 귤모찌</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1688,12 +1918,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>02.05 ~ 02.07</t>
+          <t>02.02 ~ 02.05</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9088</t>
+          <t>https://www.wishbunny.me/drop/9814</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1940,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>에블로히아 올리브오일</t>
+          <t>무항생제 한우 곰국</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1715,12 +1950,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>02.05 ~ 02.10</t>
+          <t>02.09 ~ 02.11</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9074</t>
+          <t>https://www.wishbunny.me/drop/9795</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1972,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>에브리유 큐브</t>
+          <t>감하다 감 곶감</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1742,12 +1982,17 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>02.25 ~ 02.28</t>
+          <t>02.06 ~ 02.08</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9070</t>
+          <t>https://www.wishbunny.me/drop/9779</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1759,7 +2004,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>곡물도감</t>
+          <t>붙이는 화이트보드</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1769,12 +2014,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>02.26 ~ 02.25</t>
+          <t>02.26 ~ 02.28</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9149</t>
+          <t>https://www.wishbunny.me/drop/9873</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1786,7 +2036,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>조브스 슬림맥스</t>
+          <t>아소부 신상 미니(키링) 텀블러</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1796,12 +2046,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>02.19 ~ 02.25</t>
+          <t>02.24 ~ 02.26</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9148</t>
+          <t>https://www.wishbunny.me/drop/9872</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1813,7 +2068,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>자페라노 피나</t>
+          <t>매직행거 (new 컬러 출시)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -1823,12 +2078,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>02.09 ~ 02.12</t>
+          <t>02.19 ~ 02.21</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9146</t>
+          <t>https://www.wishbunny.me/drop/9869</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1840,7 +2100,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>벨레다</t>
+          <t>샤토에르 슬라이딩선반</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1850,12 +2110,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>02.05 ~ 02.08</t>
+          <t>02.11 ~ 02.15</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9145</t>
+          <t>https://www.wishbunny.me/drop/9835</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1867,7 +2132,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>까꿍선반</t>
+          <t>미스터데코 빨래바구니</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1877,12 +2142,17 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>02.23 ~ 02.25</t>
+          <t>02.10 ~ 02.13</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9143</t>
+          <t>https://www.wishbunny.me/drop/9834</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1894,7 +2164,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>포:옹 해먹 2차/ 쿠션 옵션 추가</t>
+          <t>매직행거</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1904,12 +2174,17 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>02.18 ~ 02.20</t>
+          <t>02.26 ~ 02.28</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9142</t>
+          <t>https://www.wishbunny.me/drop/9830</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1921,7 +2196,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>아메리칸플로어 러그</t>
+          <t>주니 숟가락&amp;포크 모음전</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -1931,12 +2206,17 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>02.09 ~ 02.12</t>
+          <t>02.20 ~ 02.22</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9141</t>
+          <t>https://www.wishbunny.me/drop/9828</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1948,7 +2228,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>씨밀렉스 수납장</t>
+          <t>5단계 수처리 연수기</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -1958,12 +2238,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>02.02 ~ 02.05</t>
+          <t>03.02 ~ 03.04</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9139</t>
+          <t>https://www.wishbunny.me/drop/9822</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -1975,22 +2260,27 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>음식물분쇄기 쾌존 2차!!</t>
+          <t>(뱅네프) 바디워시&amp;향수비누</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>02.04 ~ 02.06</t>
+          <t>02.02 ~ 02.07</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9137</t>
+          <t>https://www.wishbunny.me/drop/9816</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2002,7 +2292,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>푸르름 강화 소창 수건 세트</t>
+          <t>루솔 올리올리</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2012,12 +2302,17 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>02.09 ~ 02.11</t>
+          <t>02.26 ~ 02.28</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9136</t>
+          <t>https://www.wishbunny.me/drop/9812</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2324,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>제주생선</t>
+          <t>소중한습관</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2039,12 +2334,17 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>02.06 ~ 02.08</t>
+          <t>02.24 ~ 02.26</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9129</t>
+          <t>https://www.wishbunny.me/drop/9811</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2356,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>바라짜 브레빌밤비노</t>
+          <t>방수파우치</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2071,7 +2371,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9128</t>
+          <t>https://www.wishbunny.me/drop/9800</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2083,22 +2388,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>사파dvd 플레이어</t>
+          <t>(에어딕) 미니 마사지건&amp;종아리 마사지기</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>99,000</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>02.05 ~ 02.08</t>
+          <t>02.05 ~ 02.07</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9152</t>
+          <t>https://www.wishbunny.me/drop/9818</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2420,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>메쉬넵 네블라이저</t>
+          <t>네블라이저</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2120,12 +2430,17 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>02.03 ~ 02.05</t>
+          <t>02.05 ~ 02.07</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9059</t>
+          <t>https://www.wishbunny.me/drop/9801</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2137,22 +2452,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>고요아 PTC 온풍기</t>
+          <t>스테나 가열식 가습기 2차</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>168,000</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>01.29 ~ 02.06</t>
+          <t>02.05 ~ 02.09</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8983</t>
+          <t>https://www.wishbunny.me/drop/9763</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2164,22 +2484,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>로이첸 아이지글 롤팬</t>
+          <t>미니 디지털카메라</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>89,900</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>01.28 ~ 02.01</t>
+          <t>02.26 ~ 02.28</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8957</t>
+          <t>https://www.wishbunny.me/drop/9760</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2191,22 +2516,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>마이쿠커 두유제조기</t>
+          <t>쿠진아트 에어프라이어</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>129,000</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>02.23 ~ 02.26</t>
+          <t>02.23 ~ 02.25</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8939</t>
+          <t>https://www.wishbunny.me/drop/9757</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2218,22 +2548,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>롤팬 NEW 오리지널</t>
+          <t>셀루엣 돌돌이 마사지기</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>94,000</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>01.23 ~ 02.01</t>
+          <t>02.04 ~ 02.06</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8850</t>
+          <t>https://www.wishbunny.me/drop/9750</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2245,22 +2580,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>아이리스 방역기 피톤치드2L SET</t>
+          <t>아가드 라벨프린터기</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>01.28 ~ 01.31</t>
+          <t>02.16 ~ 02.18</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8798</t>
+          <t>https://www.wishbunny.me/drop/9686</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2272,22 +2612,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>올무빙 모션쇼파 4세대</t>
+          <t>디디오랩 의류관리기</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>990,000</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>01.23 ~ 01.27</t>
+          <t>02.27 ~ 03.01</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8773</t>
+          <t>https://www.wishbunny.me/drop/9665</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2299,22 +2644,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>닌자 프로페셔널 초퍼 NJ1001KR</t>
+          <t>캐논 복합기</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>49,900</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>01.27 ~ 01.31</t>
+          <t>02.20 ~ 02.22</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8575</t>
+          <t>https://www.wishbunny.me/drop/9660</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2326,22 +2676,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>고요아 가습기</t>
+          <t>베베노 콧물흡입기</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>228,000</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>01.12 ~ 01.15</t>
+          <t>02.09 ~ 02.11</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8400</t>
+          <t>https://www.wishbunny.me/drop/9555</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2708,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>오브제히터</t>
+          <t>마이쿠커 이유식 제조기 3차</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2363,12 +2718,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>01.07 ~ 01.11</t>
+          <t>02.18 ~ 02.20</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8392</t>
+          <t>https://www.wishbunny.me/drop/9479</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2380,22 +2740,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>맥세이프 보조베터리</t>
+          <t>메쉬넵 네블라이저</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>29,900</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>01.06 ~ 01.12</t>
+          <t>02.03 ~ 02.05</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8385</t>
+          <t>https://www.wishbunny.me/drop/9456</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2772,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>틴더버드</t>
+          <t>허니스킨 12차</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2417,12 +2782,17 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>02.19 ~ 02.22</t>
+          <t>02.27 ~ 03.01</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9093</t>
+          <t>https://www.wishbunny.me/drop/9874</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2804,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>리에종드로렌 인피니트 유스 크림* 리필</t>
+          <t>(세벨리아) 핸드크림 2+1 이벤트</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2444,12 +2814,17 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>02.23 ~ 03.01</t>
+          <t>02.12 ~ 02.18</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9082</t>
+          <t>https://www.wishbunny.me/drop/9819</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2461,22 +2836,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>쁘띠스카프</t>
+          <t>립타투</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>01.29 ~ 02.02</t>
+          <t>02.25 ~ 02.27</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8882</t>
+          <t>https://www.wishbunny.me/drop/9759</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2488,22 +2868,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>밀잇 단백질 쉐이크</t>
+          <t>뉴로볼, 스틱, 발가락교정기</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>32,900</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>01.22 ~ 01.24</t>
+          <t>02.18 ~ 03.20</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8788</t>
+          <t>https://www.wishbunny.me/drop/9755</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2515,22 +2900,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>솔리디아 압박스타킹</t>
+          <t>라라메드 엉덩이 클렌저</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>02.02 ~ 02.04</t>
+          <t>02.04 ~ 02.07</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8769</t>
+          <t>https://www.wishbunny.me/drop/9636</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2542,22 +2932,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>비비러쉬 빗는 염색약! 재사용가능!</t>
+          <t>보미 다이어트 환, 디톡스 환</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>01.17 ~ 01.20</t>
+          <t>02.23 ~ 02.28</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8710</t>
+          <t>https://www.wishbunny.me/drop/9627</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2964,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AHAVA 아하바 기절세럼</t>
+          <t>효소라이너</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2579,12 +2974,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>01.05 ~ 01.11</t>
+          <t>02.19 ~ 02.22</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8558</t>
+          <t>https://www.wishbunny.me/drop/9626</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2996,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>누트라코스</t>
+          <t>디톡스 빼빼주스</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2606,12 +3006,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>01.01 ~ 01.07</t>
+          <t>02.02 ~ 02.08</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8557</t>
+          <t>https://www.wishbunny.me/drop/9625</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2623,7 +3028,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>소디살롱 켈렌 향기템</t>
+          <t>순수비타민C 앰플</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2633,12 +3038,17 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>01.12 ~ 01.14</t>
+          <t>02.26 ~ 02.28</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8294</t>
+          <t>https://www.wishbunny.me/drop/9624</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2650,22 +3060,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>싸이토핏 다이어트 커피</t>
+          <t>세벨리아 수딩밀크 &amp; LCE크림</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>26,000</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>01.19 ~ 01.21</t>
+          <t>02.09 ~ 02.12</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8236</t>
+          <t>https://www.wishbunny.me/drop/9620</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2677,7 +3092,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>몰버니 라메르메 앰플 &amp; 크림 카카오쇼핑 LIVE</t>
+          <t>프랭클린 인기 5종</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2687,12 +3102,17 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>01.29 ~ 01.31</t>
+          <t>02.26 ~ 02.28</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8218</t>
+          <t>https://www.wishbunny.me/drop/9483</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2704,22 +3124,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>루트헤어 앵콜 고별전</t>
+          <t>소중한 습관</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>32,400</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>01.26 ~ 01.28</t>
+          <t>02.11 ~ 02.13</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8217</t>
+          <t>https://www.wishbunny.me/drop/9477</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2731,7 +3156,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>삼소니 상하복</t>
+          <t>맘팬티&amp; 파파팬티</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2741,12 +3166,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>02.20 ~ 02.22</t>
+          <t>02.08 ~ 02.12</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9133</t>
+          <t>https://www.wishbunny.me/drop/9629</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2758,22 +3188,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>삠뽀요 봄신상</t>
+          <t>미니두두 v2 봄신상</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>02.19 ~ 02.22</t>
+          <t>02.02 ~ 02.04</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9067</t>
+          <t>https://www.wishbunny.me/drop/9618</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2785,7 +3220,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>삼소니 등원룩</t>
+          <t>NEW 디즈니 간절기 등원북</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2795,12 +3230,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>02.04 ~ 02.08</t>
+          <t>02.26 ~ 02.28</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9060</t>
+          <t>https://www.wishbunny.me/drop/9615</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2812,7 +3252,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>미니두두 스카프 VER 1&amp;3</t>
+          <t>NEW 아기스카프</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2822,12 +3262,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>02.05 ~ 02.07</t>
+          <t>02.06 ~ 02.09</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9051</t>
+          <t>https://www.wishbunny.me/drop/9608</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2839,7 +3284,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>뉴코코맘 스카프</t>
+          <t>NEW 쭈리 등원복</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2849,12 +3294,17 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>02.23 ~ 02.26</t>
+          <t>02.01 ~ 02.08</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9034</t>
+          <t>https://www.wishbunny.me/drop/9604</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2866,7 +3316,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>오우아스튜디오 시리즈 (미술가운, 앞치마, 방수파우치)</t>
+          <t>이불 상하복 세트</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -2876,12 +3326,17 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>02.10 ~ 02.12</t>
+          <t>02.16 ~ 02.18</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9028</t>
+          <t>https://www.wishbunny.me/drop/9509</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2893,7 +3348,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>졸리쇼즈</t>
+          <t>실내복 고쟁이 등*</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2903,12 +3358,17 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>02.05 ~ 02.08</t>
+          <t>02.19 ~ 02.21</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9025</t>
+          <t>https://www.wishbunny.me/drop/9480</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2920,7 +3380,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>실내복&amp;고쟁이</t>
+          <t>시크릿키즈 상하복</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -2930,12 +3390,17 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>02.09 ~ 02.11</t>
+          <t>02.03 ~ 02.05</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9006</t>
+          <t>https://www.wishbunny.me/drop/9471</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2947,22 +3412,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>데일리라이크 키즈패션</t>
+          <t>삠뽀유 봄신상</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>01.27 ~ 01.30</t>
+          <t>02.19 ~ 02.22</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8971</t>
+          <t>https://www.wishbunny.me/drop/9464</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -2974,22 +3444,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>누아 프리미엄 아동복</t>
+          <t>삼소니 등원룩</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>01.28 ~ 02.01</t>
+          <t>02.04 ~ 02.08</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8917</t>
+          <t>https://www.wishbunny.me/drop/9457</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3001,22 +3476,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>리틀피기 봄신상</t>
+          <t>어뜌 휴대용 기저귀 봉투 케어백</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>14,000</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>02.09 ~ 02.12</t>
+          <t>02.27 ~ 03.01</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8861</t>
+          <t>https://www.wishbunny.me/drop/9407</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3508,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>리뗀클로르 턱받이 모음전</t>
+          <t>뉴코코맘 유아 스카프</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3038,12 +3518,17 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>02.09 ~ 02.12</t>
+          <t>02.19 ~ 02.22</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8846</t>
+          <t>https://www.wishbunny.me/drop/9405</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3055,22 +3540,27 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>롱키원프리미엄골드공구첫런칭</t>
+          <t>슈퍼세이브 곰보배추시럽</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>77,000</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>01.12 ~ 02.10</t>
+          <t>02.13 ~ 02.19</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9109</t>
+          <t>https://www.wishbunny.me/drop/9895</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3572,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>더리틀스 케이투미네랄부스터</t>
+          <t>랩트리션 그로우업 플러스 초유</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3092,12 +3582,17 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>02.20 ~ 02.22</t>
+          <t>02.24 ~ 02.28</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9101</t>
+          <t>https://www.wishbunny.me/drop/9885</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3604,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>제니튼</t>
+          <t>VSL #3 유산균</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3119,12 +3614,17 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>02.18 ~ 02.20</t>
+          <t>02.19 ~ 02.22</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9100</t>
+          <t>https://www.wishbunny.me/drop/9884</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3636,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>트루엔 사르르 리포좀 비타민C &amp; 메가리포좀 비타민C</t>
+          <t>마그오메가 DHA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3146,12 +3646,17 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>02.12 ~ 02.14</t>
+          <t>02.05 ~ 02.09</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9099</t>
+          <t>https://www.wishbunny.me/drop/9883</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3163,22 +3668,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>더좋은 이뮤업 그로우</t>
+          <t>다이어트환</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>129,360</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>02.07 ~ 02.09</t>
+          <t>02.02 ~ 02.05</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9098</t>
+          <t>https://www.wishbunny.me/drop/9851</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3700,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>건강나눔 아이마음 햄철 &amp; 베타글루칸</t>
+          <t>리포좀비타민C</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3200,12 +3710,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>02.05 ~ 02.07</t>
+          <t>02.19</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9097</t>
+          <t>https://www.wishbunny.me/drop/9845</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3217,22 +3732,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>YDY 폴라조임계오메가3</t>
+          <t>올퓨어멀티비타민</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>31,000</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>02.02 ~ 02.04</t>
+          <t>02.02 ~ 02.08</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9096</t>
+          <t>https://www.wishbunny.me/drop/9839</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3764,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>어섬키즈 오메가3 &amp; 어섬CM</t>
+          <t>온 가족 변Bi 탈출템</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3254,12 +3774,17 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>02.01 ~ 02.03</t>
+          <t>02.23 ~ 02.25</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9095</t>
+          <t>https://www.wishbunny.me/drop/9821</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3796,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>K3 유산균 선물세트</t>
+          <t>리포좀 글루타치온</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3281,12 +3806,17 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>02.02 ~ 02.04</t>
+          <t>02.19 ~ 02.21</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9087</t>
+          <t>https://www.wishbunny.me/drop/9820</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3828,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>마이너스 티 프리미엄</t>
+          <t>헤모키즈</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3308,12 +3838,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>02.19 ~ 03.01</t>
+          <t>02.13 ~ 02.15</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9081</t>
+          <t>https://www.wishbunny.me/drop/9807</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3325,7 +3860,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>페이퍼백 글루타치온 2종</t>
+          <t>굿에바스 플레이짐</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3335,12 +3870,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>02.19 ~ 03.01</t>
+          <t>02.13 ~ 02.15</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9080</t>
+          <t>https://www.wishbunny.me/drop/9782</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3892,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>뮴 키즈 오메가3 구미</t>
+          <t>아이언츄 철분</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3362,12 +3902,17 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>02.12 ~ 02.18</t>
+          <t>02.26 ~ 02.28</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9079</t>
+          <t>https://www.wishbunny.me/drop/9772</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3389,12 +3934,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>01.30 ~ 01.31</t>
+          <t>01.31 ~ 01.31</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>https://www.wishbunny.me/drop/8903</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3424,6 +3974,11 @@
           <t>https://www.wishbunny.me/drop/8365</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3451,6 +4006,11 @@
           <t>https://www.wishbunny.me/drop/7582</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3478,6 +4038,11 @@
           <t>https://www.wishbunny.me/drop/7580</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3497,12 +4062,17 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>01.27 ~ 01.31</t>
+          <t>01.31 ~ 02.05</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>https://www.wishbunny.me/drop/7135</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3532,6 +4102,11 @@
           <t>https://www.wishbunny.me/drop/6881</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3559,6 +4134,11 @@
           <t>https://www.wishbunny.me/drop/6877</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3586,6 +4166,11 @@
           <t>https://www.wishbunny.me/drop/6637</t>
         </is>
       </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3613,6 +4198,11 @@
           <t>https://www.wishbunny.me/drop/6635</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3640,6 +4230,11 @@
           <t>https://www.wishbunny.me/drop/6632</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3667,6 +4262,11 @@
           <t>https://www.wishbunny.me/drop/6628</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3694,6 +4294,11 @@
           <t>https://www.wishbunny.me/drop/6623</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3703,22 +4308,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>트래블백</t>
+          <t>마이다스 호텔&amp;리조트 클래스 1+1 최초</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>02.02 ~ 02.04</t>
+          <t>02.02 ~ 02.08</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8918</t>
+          <t>https://www.wishbunny.me/drop/9583</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3730,7 +4340,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>소피텔 앰배서더 서울 특가</t>
+          <t>롤링힐스 2026 하리보룸 최초 공구</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3740,12 +4350,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>01.26 ~ 01.30</t>
+          <t>02.03 ~ 02.06</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8890</t>
+          <t>https://www.wishbunny.me/drop/9503</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3757,22 +4372,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>위로 여는 풀메탈 알루미늄 캐리어 머즈캐리어</t>
+          <t>트래블백</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>115,000</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>01.22 ~ 01.31</t>
+          <t>02.02 ~ 02.04</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8691</t>
+          <t>https://www.wishbunny.me/drop/8918</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3784,7 +4404,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>캐리어</t>
+          <t>소피텔 앰배서더 서울 특가</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3794,12 +4414,17 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>01.27 ~ 01.31</t>
+          <t>01.26 ~ 01.30</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8567</t>
+          <t>https://www.wishbunny.me/drop/8890</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3811,22 +4436,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>제주 신라호텔 역대급 특가</t>
+          <t>위로 여는 풀메탈 알루미늄 캐리어 머즈캐리어</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>115,000</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>01.12 ~ 01.18</t>
+          <t>01.25 ~ 02.02</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8461</t>
+          <t>https://www.wishbunny.me/drop/8691</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3838,22 +4468,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>목베개 (스탠다드 / 프리미엄</t>
+          <t>캐리어</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>18,800</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>01.12 ~ 01.18</t>
+          <t>01.27 ~ 01.31</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8351</t>
+          <t>https://www.wishbunny.me/drop/8567</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3865,7 +4500,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>유누옷장×머즈캐리어 파일럿캐리어 기내용캐리어</t>
+          <t>제주 신라호텔 역대급 특가</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -3875,12 +4510,17 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>01.05 ~ 01.08</t>
+          <t>01.12 ~ 01.18</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8127</t>
+          <t>https://www.wishbunny.me/drop/8461</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3892,22 +4532,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>보홀 에어텔공구</t>
+          <t>목베개 (스탠다드 / 프리미엄</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>549,000</t>
+          <t>18,800</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>01.14 ~ 01.16</t>
+          <t>01.12 ~ 01.18</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8105</t>
+          <t>https://www.wishbunny.me/drop/8351</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3919,7 +4564,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>속초 롯데리조트 특가</t>
+          <t>유누옷장×머즈캐리어 파일럿캐리어 기내용캐리어</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -3929,12 +4574,17 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>01.05 ~ 01.11</t>
+          <t>01.05 ~ 01.08</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8075</t>
+          <t>https://www.wishbunny.me/drop/8127</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3946,22 +4596,27 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>베로로 캐리어</t>
+          <t>보홀 에어텔공구</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>199,000</t>
+          <t>549,000</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>01.28 ~ 01.31</t>
+          <t>01.14 ~ 01.16</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/7701</t>
+          <t>https://www.wishbunny.me/drop/8105</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -3973,7 +4628,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>마이다스 호텔</t>
+          <t>속초 롯데리조트 특가</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -3983,12 +4638,17 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>01.27 ~ 01.31</t>
+          <t>01.05 ~ 01.11</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/7700</t>
+          <t>https://www.wishbunny.me/drop/8075</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -4000,22 +4660,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>로드웨이 캐리어</t>
+          <t>베로로 캐리어</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>109,000</t>
+          <t>199,000</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>01.21 ~ 01.25</t>
+          <t>01.28 ~ 01.31</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/7264</t>
+          <t>https://www.wishbunny.me/drop/7701</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -4045,6 +4710,11 @@
           <t>https://www.wishbunny.me/drop/6338</t>
         </is>
       </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4072,6 +4742,11 @@
           <t>https://www.wishbunny.me/drop/6331</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4099,6 +4774,11 @@
           <t>https://www.wishbunny.me/drop/6330</t>
         </is>
       </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4126,6 +4806,11 @@
           <t>https://www.wishbunny.me/drop/4568</t>
         </is>
       </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4153,6 +4838,11 @@
           <t>https://www.wishbunny.me/drop/4390</t>
         </is>
       </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4180,6 +4870,11 @@
           <t>https://www.wishbunny.me/drop/4389</t>
         </is>
       </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4207,6 +4902,11 @@
           <t>https://www.wishbunny.me/drop/4387</t>
         </is>
       </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4234,6 +4934,11 @@
           <t>https://www.wishbunny.me/drop/4386</t>
         </is>
       </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4261,6 +4966,11 @@
           <t>https://www.wishbunny.me/drop/4385</t>
         </is>
       </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4288,6 +4998,11 @@
           <t>https://www.wishbunny.me/drop/4384</t>
         </is>
       </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4315,6 +5030,11 @@
           <t>https://www.wishbunny.me/drop/4383</t>
         </is>
       </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4342,6 +5062,11 @@
           <t>https://www.wishbunny.me/drop/4382</t>
         </is>
       </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4369,6 +5094,11 @@
           <t>https://www.wishbunny.me/drop/8643</t>
         </is>
       </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4396,6 +5126,11 @@
           <t>https://www.wishbunny.me/drop/8098</t>
         </is>
       </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4423,6 +5158,11 @@
           <t>https://www.wishbunny.me/drop/8097</t>
         </is>
       </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4450,6 +5190,11 @@
           <t>https://www.wishbunny.me/drop/6521</t>
         </is>
       </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4477,6 +5222,11 @@
           <t>https://www.wishbunny.me/drop/6490</t>
         </is>
       </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4504,6 +5254,11 @@
           <t>https://www.wishbunny.me/drop/6485</t>
         </is>
       </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4531,6 +5286,11 @@
           <t>https://www.wishbunny.me/drop/6042</t>
         </is>
       </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4558,6 +5318,11 @@
           <t>https://www.wishbunny.me/drop/5849</t>
         </is>
       </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4585,6 +5350,11 @@
           <t>https://www.wishbunny.me/drop/5554</t>
         </is>
       </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4612,6 +5382,11 @@
           <t>https://www.wishbunny.me/drop/5541</t>
         </is>
       </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4639,6 +5414,11 @@
           <t>https://www.wishbunny.me/drop/5483</t>
         </is>
       </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4666,6 +5446,11 @@
           <t>https://www.wishbunny.me/drop/5252</t>
         </is>
       </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>New Item</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4675,7 +5460,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>맥킹덤 맥타일즈</t>
+          <t>NEW item Coming soon</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4685,12 +5470,17 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>02.02 ~ 02.06</t>
+          <t>02.12 ~ 02.15</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9058</t>
+          <t>https://www.wishbunny.me/drop/9621</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -4702,7 +5492,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>애플비 스티커북</t>
+          <t>윈덤 강원 고성 with CJ</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4712,12 +5502,17 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>02.06 ~ 02.08</t>
+          <t>02.23 ~ 02.26</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/9052</t>
+          <t>https://www.wishbunny.me/drop/9511</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -4729,22 +5524,27 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>정품 유키오 인형키링(키티/교동)</t>
+          <t>특별 기획전</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>01.25 ~ 02.28</t>
+          <t>02.04 ~ 02.06</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8876</t>
+          <t>https://www.wishbunny.me/drop/9268</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -4756,22 +5556,27 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>뉴케어 마이키즈</t>
+          <t>특별 기획전</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>28,900</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>01.22 ~ 02.08</t>
+          <t>02.04 ~ 02.06</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8620</t>
+          <t>https://www.wishbunny.me/drop/9194</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -4783,7 +5588,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>곰보배추시럽</t>
+          <t>애플비 스티커북</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4793,12 +5598,17 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>02.12 ~ 02.26</t>
+          <t>02.06 ~ 02.08</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8597</t>
+          <t>https://www.wishbunny.me/drop/9052</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -4810,22 +5620,27 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>미태그</t>
+          <t>정품 유키오 인형키링(키티/교동)</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>01.12 ~ 01.18</t>
+          <t>01.25 ~ 02.28</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8456</t>
+          <t>https://www.wishbunny.me/drop/8876</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -4837,22 +5652,27 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>에스파뇰라 오일세트 설선물</t>
+          <t>뉴케어 마이키즈</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>20,500</t>
+          <t>28,900</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>01.26 ~ 01.31</t>
+          <t>02.02 ~ 02.18</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8347</t>
+          <t>https://www.wishbunny.me/drop/8620</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -4864,22 +5684,27 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>드라이 수채화 (최초)</t>
+          <t>곰보배추시럽</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>14,800</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>01.05 ~ 01.05</t>
+          <t>02.12 ~ 02.26</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8331</t>
+          <t>https://www.wishbunny.me/drop/8597</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -4891,22 +5716,27 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>모에모에 라벨프린터기 무선네임스티커기계</t>
+          <t>미태그</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>15,000</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>01.21 ~ 01.25</t>
+          <t>01.12 ~ 01.18</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/8064</t>
+          <t>https://www.wishbunny.me/drop/8456</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -4918,22 +5748,27 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>540g 경량 방수 책가방 2종세트 모노라이트 워셔블 초등학생 저학년 백팩 여아 남아</t>
+          <t>에스파뇰라 오일세트 설선물</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>129,000</t>
+          <t>20,500</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>01.22 ~ 01.24</t>
+          <t>01.26 ~ 01.31</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/7887</t>
+          <t>https://www.wishbunny.me/drop/8347</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -4945,22 +5780,27 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>쾌걸조로리</t>
+          <t>드라이 수채화 (최초)</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>110,600</t>
+          <t>14,800</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>01.13 ~ 01.15</t>
+          <t>01.05 ~ 01.05</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/7859</t>
+          <t>https://www.wishbunny.me/drop/8331</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
@@ -4972,22 +5812,27 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>미니결과 함께 하는 미니미 다이어트! 미미다 10기</t>
+          <t>모에모에 라벨프린터기 무선네임스티커기계</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>420,500</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>01.05 ~ 01.11</t>
+          <t>01.21 ~ 01.25</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>https://www.wishbunny.me/drop/7728</t>
+          <t>https://www.wishbunny.me/drop/8064</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>New Item</t>
         </is>
       </c>
     </row>
